--- a/artfynd/A 45109-2024 artfynd.xlsx
+++ b/artfynd/A 45109-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109838471</v>
+        <v>109838474</v>
       </c>
       <c r="B6" t="n">
-        <v>88476</v>
+        <v>78098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541894.0405560075</v>
+        <v>541906.5698652434</v>
       </c>
       <c r="R6" t="n">
-        <v>6968451.697756562</v>
+        <v>6968402.060274301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109838474</v>
+        <v>109838475</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
+        <v>77259</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541906.5698652434</v>
+        <v>541964.5756301113</v>
       </c>
       <c r="R7" t="n">
-        <v>6968402.060274301</v>
+        <v>6968409.655062034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109838475</v>
+        <v>109838473</v>
       </c>
       <c r="B8" t="n">
-        <v>77259</v>
+        <v>89611</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>5260</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541964.5756301113</v>
+        <v>541873.5999874555</v>
       </c>
       <c r="R8" t="n">
-        <v>6968409.655062034</v>
+        <v>6968404.380236602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109838472</v>
+        <v>109838476</v>
       </c>
       <c r="B9" t="n">
-        <v>90841</v>
+        <v>94121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541894.0405560075</v>
+        <v>541982.3392821709</v>
       </c>
       <c r="R9" t="n">
-        <v>6968451.697756562</v>
+        <v>6968415.82164702</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,230 +1568,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>109838473</v>
-      </c>
-      <c r="B10" t="n">
-        <v>89611</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5260</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lateritticka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Postia lateritia</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Renvall</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Storabborselsberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>541873.5999874555</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6968404.380236602</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>109838476</v>
-      </c>
-      <c r="B11" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>53</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Storabborselsberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>541982.3392821709</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6968415.82164702</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45109-2024 artfynd.xlsx
+++ b/artfynd/A 45109-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109276019</v>
+        <v>109838476</v>
       </c>
       <c r="B2" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor Abborselberget, Jmt</t>
+          <t>Storabborselsberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541893.12571221</v>
+        <v>541983</v>
       </c>
       <c r="R2" t="n">
-        <v>6968451.686067717</v>
+        <v>6968416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,12 +775,7 @@
         <v>109276018</v>
       </c>
       <c r="B3" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541893.12571221</v>
+        <v>541893</v>
       </c>
       <c r="R3" t="n">
-        <v>6968451.686067717</v>
+        <v>6968452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109276020</v>
+        <v>109838471</v>
       </c>
       <c r="B4" t="n">
-        <v>89611</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5260</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor Abborselberget, Jmt</t>
+          <t>Storabborselsberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541870.3571571888</v>
+        <v>541894</v>
       </c>
       <c r="R4" t="n">
-        <v>6968407.536855482</v>
+        <v>6968452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109838477</v>
+        <v>109276019</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storabborselsberget, Jmt</t>
+          <t>Stor Abborselberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541937.6843052008</v>
+        <v>541893</v>
       </c>
       <c r="R5" t="n">
-        <v>6968473.270959101</v>
+        <v>6968452</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109838474</v>
+        <v>109838472</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541906.5698652434</v>
+        <v>541894</v>
       </c>
       <c r="R6" t="n">
-        <v>6968402.060274301</v>
+        <v>6968452</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,62 +1148,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109838475</v>
+        <v>109276020</v>
       </c>
       <c r="B7" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>5260</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storabborselsberget, Jmt</t>
+          <t>Stor Abborselberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541964.5756301113</v>
+        <v>541871</v>
       </c>
       <c r="R7" t="n">
-        <v>6968409.655062034</v>
+        <v>6968407</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,12 +1245,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1350,12 +1260,7 @@
         <v>109838473</v>
       </c>
       <c r="B8" t="n">
-        <v>89611</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541873.5999874555</v>
+        <v>541873</v>
       </c>
       <c r="R8" t="n">
-        <v>6968404.380236602</v>
+        <v>6968405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109838476</v>
+        <v>109838474</v>
       </c>
       <c r="B9" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541982.3392821709</v>
+        <v>541907</v>
       </c>
       <c r="R9" t="n">
-        <v>6968415.82164702</v>
+        <v>6968402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2023-05-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,15 +1439,209 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>109838477</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storabborselsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>541938</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6968473</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>109838475</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storabborselsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>541964</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6968410</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
